--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5389" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5389" uniqueCount="474">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T05:36:05+00:00</t>
+    <t>2026-07-29T08:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -908,7 +908,7 @@
     <t>Observation.languageCode</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/all-languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Observation.value</t>
@@ -984,9 +984,6 @@
   </si>
   <si>
     <t>Observation.interpretationCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Interprétation </t>
   </si>
   <si>
     <t>Interprétation</t>
@@ -11677,7 +11674,7 @@
         <v>316</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11708,7 +11705,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>75</v>
@@ -11746,10 +11743,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11805,7 +11802,7 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>75</v>
@@ -11823,7 +11820,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -11843,10 +11840,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11873,7 +11870,7 @@
       </c>
       <c r="L99" s="2"/>
       <c r="M99" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11924,7 +11921,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -11944,10 +11941,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11970,7 +11967,7 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -12023,7 +12020,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -12043,10 +12040,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12069,7 +12066,7 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -12122,7 +12119,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -12142,10 +12139,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12168,7 +12165,7 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -12221,7 +12218,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -12241,10 +12238,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12267,7 +12264,7 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -12320,7 +12317,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -12340,10 +12337,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12366,7 +12363,7 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -12419,7 +12416,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -12439,10 +12436,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12465,7 +12462,7 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -12518,7 +12515,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -12538,10 +12535,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12564,7 +12561,7 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -12605,7 +12602,7 @@
         <v>75</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AC106" s="2"/>
       <c r="AD106" t="s" s="2">
@@ -12615,7 +12612,7 @@
         <v>125</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -12635,13 +12632,13 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C107" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="C107" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>75</v>
@@ -12663,10 +12660,10 @@
         <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
@@ -12718,7 +12715,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -12738,10 +12735,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="B108" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12839,10 +12836,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B109" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12940,10 +12937,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B110" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13041,10 +13038,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13142,10 +13139,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B112" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13245,10 +13242,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13348,10 +13345,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13451,10 +13448,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B115" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13554,10 +13551,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B116" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13655,10 +13652,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B117" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13695,7 +13692,7 @@
         <v>75</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>75</v>
@@ -13714,25 +13711,25 @@
       </c>
       <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF117" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
@@ -13752,10 +13749,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B118" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13782,7 +13779,7 @@
       </c>
       <c r="L118" s="2"/>
       <c r="M118" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -13833,7 +13830,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -13853,10 +13850,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B119" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13883,12 +13880,12 @@
       </c>
       <c r="L119" s="2"/>
       <c r="M119" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q119" s="2"/>
       <c r="R119" t="s" s="2">
@@ -13934,7 +13931,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -13954,10 +13951,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B120" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14033,7 +14030,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -14053,10 +14050,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B121" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14079,7 +14076,7 @@
         <v>75</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
@@ -14132,7 +14129,7 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -14152,10 +14149,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B122" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14178,7 +14175,7 @@
         <v>75</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
@@ -14231,7 +14228,7 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -14251,10 +14248,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14277,7 +14274,7 @@
         <v>75</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
@@ -14330,7 +14327,7 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -14350,10 +14347,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14376,7 +14373,7 @@
         <v>75</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
@@ -14429,7 +14426,7 @@
         <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -14449,10 +14446,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B125" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14475,7 +14472,7 @@
         <v>75</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
@@ -14528,7 +14525,7 @@
         <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -14548,10 +14545,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B126" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14574,7 +14571,7 @@
         <v>75</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
@@ -14627,7 +14624,7 @@
         <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -14647,10 +14644,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B127" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14673,7 +14670,7 @@
         <v>75</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
@@ -14726,7 +14723,7 @@
         <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -14746,10 +14743,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B128" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14772,7 +14769,7 @@
         <v>75</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
@@ -14825,7 +14822,7 @@
         <v>75</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -14845,10 +14842,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B129" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14871,7 +14868,7 @@
         <v>75</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -14924,7 +14921,7 @@
         <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -14944,10 +14941,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B130" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14970,7 +14967,7 @@
         <v>75</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -15023,7 +15020,7 @@
         <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -15043,10 +15040,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B131" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15069,7 +15066,7 @@
         <v>75</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
@@ -15122,7 +15119,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -15142,13 +15139,13 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C132" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="C132" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>75</v>
@@ -15170,10 +15167,10 @@
         <v>75</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
@@ -15225,7 +15222,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -15245,10 +15242,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15346,10 +15343,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15447,10 +15444,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15548,10 +15545,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15649,10 +15646,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15752,10 +15749,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15855,10 +15852,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15958,10 +15955,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16061,10 +16058,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16162,10 +16159,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16202,7 +16199,7 @@
         <v>75</v>
       </c>
       <c r="S142" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="T142" t="s" s="2">
         <v>75</v>
@@ -16221,25 +16218,25 @@
       </c>
       <c r="Y142" s="2"/>
       <c r="Z142" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF142" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>76</v>
@@ -16259,10 +16256,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16289,7 +16286,7 @@
       </c>
       <c r="L143" s="2"/>
       <c r="M143" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -16301,7 +16298,7 @@
         <v>75</v>
       </c>
       <c r="S143" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="T143" t="s" s="2">
         <v>75</v>
@@ -16340,7 +16337,7 @@
         <v>75</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -16360,10 +16357,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16390,12 +16387,12 @@
       </c>
       <c r="L144" s="2"/>
       <c r="M144" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q144" s="2"/>
       <c r="R144" t="s" s="2">
@@ -16441,7 +16438,7 @@
         <v>75</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
@@ -16461,10 +16458,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16540,7 +16537,7 @@
         <v>75</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -16560,10 +16557,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16586,7 +16583,7 @@
         <v>75</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
@@ -16639,7 +16636,7 @@
         <v>75</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -16659,10 +16656,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16685,7 +16682,7 @@
         <v>75</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="L147" s="2"/>
       <c r="M147" s="2"/>
@@ -16738,7 +16735,7 @@
         <v>75</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -16758,10 +16755,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16784,7 +16781,7 @@
         <v>75</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="L148" s="2"/>
       <c r="M148" s="2"/>
@@ -16837,7 +16834,7 @@
         <v>75</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>81</v>
@@ -16857,10 +16854,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16883,7 +16880,7 @@
         <v>75</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L149" s="2"/>
       <c r="M149" s="2"/>
@@ -16936,7 +16933,7 @@
         <v>75</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
@@ -16956,10 +16953,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -16982,7 +16979,7 @@
         <v>75</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L150" s="2"/>
       <c r="M150" s="2"/>
@@ -17035,7 +17032,7 @@
         <v>75</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -17055,10 +17052,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17081,7 +17078,7 @@
         <v>75</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L151" s="2"/>
       <c r="M151" s="2"/>
@@ -17134,7 +17131,7 @@
         <v>75</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -17154,10 +17151,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17180,7 +17177,7 @@
         <v>75</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
@@ -17233,7 +17230,7 @@
         <v>75</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -17253,10 +17250,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17279,7 +17276,7 @@
         <v>75</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
@@ -17332,7 +17329,7 @@
         <v>75</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
@@ -17352,10 +17349,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17378,7 +17375,7 @@
         <v>75</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
@@ -17431,7 +17428,7 @@
         <v>75</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -17451,10 +17448,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17477,7 +17474,7 @@
         <v>75</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
@@ -17530,7 +17527,7 @@
         <v>75</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -17550,10 +17547,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17576,7 +17573,7 @@
         <v>75</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L156" s="2"/>
       <c r="M156" s="2"/>
@@ -17629,7 +17626,7 @@
         <v>75</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -17649,10 +17646,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17675,7 +17672,7 @@
         <v>75</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
@@ -17728,7 +17725,7 @@
         <v>75</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -17748,10 +17745,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17774,7 +17771,7 @@
         <v>75</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
@@ -17827,7 +17824,7 @@
         <v>75</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -17847,10 +17844,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17873,7 +17870,7 @@
         <v>75</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
@@ -17926,7 +17923,7 @@
         <v>75</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
@@ -17946,10 +17943,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -17972,11 +17969,11 @@
         <v>75</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L160" s="2"/>
       <c r="M160" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -18027,7 +18024,7 @@
         <v>75</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
@@ -18047,10 +18044,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18148,10 +18145,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18249,10 +18246,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18350,10 +18347,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18451,10 +18448,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18554,10 +18551,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18657,10 +18654,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18760,10 +18757,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18863,10 +18860,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -18964,10 +18961,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19001,7 +18998,7 @@
       </c>
       <c r="Q170" s="2"/>
       <c r="R170" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="S170" t="s" s="2">
         <v>75</v>
@@ -19023,7 +19020,7 @@
       </c>
       <c r="Y170" s="2"/>
       <c r="Z170" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>75</v>
@@ -19041,7 +19038,7 @@
         <v>75</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
@@ -19061,10 +19058,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19087,7 +19084,7 @@
         <v>75</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
@@ -19140,7 +19137,7 @@
         <v>75</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>76</v>
@@ -19160,10 +19157,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19186,7 +19183,7 @@
         <v>75</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
@@ -19239,7 +19236,7 @@
         <v>75</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:04:35+00:00</t>
+    <t>2026-07-29T08:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:58:09+00:00</t>
+    <t>2026-07-29T09:37:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:37:21+00:00</t>
+    <t>2026-08-03T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
